--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/ARKANSAS_2015.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/ARKANSAS_2015.xlsx
@@ -2796,7 +2796,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C136">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C235">
@@ -11580,7 +11580,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C624">
@@ -11922,7 +11922,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C643">
